--- a/www/ig/fhir/ror/StructureDefinition-ror-location.xlsx
+++ b/www/ig/fhir/ror/StructureDefinition-ror-location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$135</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4705" uniqueCount="745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4775" uniqueCount="761">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T09:54:01+00:00</t>
+    <t>2026-04-29T15:35:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
@@ -658,6 +658,9 @@
     <t>Extension créée dans le cadre du ROR pour représenter le code officiel géographique (COG) de la commune dans laquelle le lieu est situé.</t>
   </si>
   <si>
+    <t>CommuneCog</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-equipment</t>
   </si>
   <si>
@@ -675,6 +678,9 @@
  Device représente une instance d'un équipement alors l'équipement pour le ROR correspond juste au nombre d'équipement de même type.</t>
   </si>
   <si>
+    <t>EquipementSpecifique</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-residential-capacity</t>
   </si>
   <si>
@@ -691,6 +697,9 @@
     <t>Extension créée dans le cadre du ROR qui décrit un type d'habitation adapté à la réalisation d'une offre.</t>
   </si>
   <si>
+    <t>CapaciteHabitation</t>
+  </si>
+  <si>
     <t>Location.extension:ror-location-supported-capacity</t>
   </si>
   <si>
@@ -707,6 +716,9 @@
     <t>Extension créée dans le cadre du ROR qui indique une série d’enregistrements indiquant la quantité de lit (ou de place) de l'entité pour un statut et une temporalité donnés.</t>
   </si>
   <si>
+    <t>CapacitePriseCharge</t>
+  </si>
+  <si>
     <t>Location.extension:ror-meta-creation-date</t>
   </si>
   <si>
@@ -723,6 +735,44 @@
     <t>Extension créée dans le cadre du ROR qui correspond à la date de création (dans le ROR régional) présente dans les métadonnées.</t>
   </si>
   <si>
+    <t>metadonnee.dateCreation</t>
+  </si>
+  <si>
+    <t>Location.extension:ror-meta-questionnaire-used-as-a-template</t>
+  </si>
+  <si>
+    <t>ror-meta-questionnaire-used-as-a-template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/ror/StructureDefinition/ror-meta-questionnaire-used-as-a-template}
+</t>
+  </si>
+  <si>
+    <t>modeleSaisie (Metadonnee) : Référence canonique vers le questionnaire utilisé comme modèle de saisie, incluant obligatoirement la version sous la forme url|version. Exemple : https://interop.esante.gouv.fr/ig/fhir/ror/Questionnaire/ror-questionnaire-2042|1</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre du ROR qui correspond au questionnaire de saisie utilisé comme modèle associé à la ressource.</t>
+  </si>
+  <si>
+    <t>metadonnee.modeleSaisie</t>
+  </si>
+  <si>
+    <t>Location.extension:ror-comment</t>
+  </si>
+  <si>
+    <t>ror-comment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/ror/StructureDefinition/ror-comment}
+</t>
+  </si>
+  <si>
+    <t>commentaire (LieuRealisationOffre) : Commentaire qui permet à la structure de donner des informations complémentaires</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre du ROR pour décrire le commentaire qui permet à la structure de donner des informations complémentaires</t>
+  </si>
+  <si>
     <t>Location.modifierExtension</t>
   </si>
   <si>
@@ -1490,7 +1540,7 @@
     <t>ContactPoint.value</t>
   </si>
   <si>
-    <t>adresseTelecom</t>
+    <t>telecommunication.adresseTelecom</t>
   </si>
   <si>
     <t>./url</t>
@@ -2189,7 +2239,7 @@
 </t>
   </si>
   <si>
-    <t>Organization responsible for provisioning and upkeep</t>
+    <t>Hors périmètre du modèle d'exposition du ROR, ce champ est utilisé dans le cas suivant : le Lieu de Réalisation (Location) n'est rattaché à aucune Offre Opérationnelle (HealthcareService), la Location ne pourra alors être rattachée qu'à un ou des HealthcareServices ayant comme parent cette Organization qui doit obligatoirement être une EG</t>
   </si>
   <si>
     <t>The organization responsible for the provisioning and upkeep of the location.</t>
@@ -2637,12 +2687,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM133"/>
+  <dimension ref="A1:AM135"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.98046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="34.48828125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="40.8828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4780,7 +4830,7 @@
         <v>118</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>75</v>
@@ -4791,13 +4841,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>75</v>
@@ -4819,13 +4869,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4891,7 +4941,7 @@
         <v>118</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -4902,13 +4952,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>75</v>
@@ -4930,13 +4980,13 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5002,7 +5052,7 @@
         <v>118</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>75</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>75</v>
@@ -5013,13 +5063,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>75</v>
@@ -5041,13 +5091,13 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5113,7 +5163,7 @@
         <v>118</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>75</v>
@@ -5124,13 +5174,13 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -5152,13 +5202,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5224,7 +5274,7 @@
         <v>118</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -5235,46 +5285,44 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>75</v>
       </c>
@@ -5310,19 +5358,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -5337,10 +5385,10 @@
         <v>118</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -5348,12 +5396,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
@@ -5362,7 +5412,7 @@
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>86</v>
@@ -5371,21 +5421,19 @@
         <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -5421,17 +5469,19 @@
         <v>75</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5443,59 +5493,59 @@
         <v>98</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I26" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>232</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -5532,19 +5582,19 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5556,24 +5606,24 @@
         <v>98</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>237</v>
+        <v>101</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5584,28 +5634,30 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>105</v>
+        <v>250</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -5641,82 +5693,82 @@
         <v>75</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="D28" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -5752,19 +5804,19 @@
         <v>75</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5776,24 +5828,24 @@
         <v>98</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>101</v>
+        <v>253</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5810,26 +5862,22 @@
         <v>75</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -5853,13 +5901,13 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -5877,7 +5925,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5886,16 +5934,16 @@
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -5903,46 +5951,44 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
       </c>
@@ -5966,49 +6012,49 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>101</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>75</v>
@@ -6016,10 +6062,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6036,22 +6082,26 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
@@ -6075,13 +6125,13 @@
         <v>75</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>75</v>
+        <v>269</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>75</v>
@@ -6099,7 +6149,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -6108,16 +6158,16 @@
         <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>75</v>
@@ -6125,44 +6175,46 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>274</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
@@ -6186,49 +6238,49 @@
         <v>75</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>75</v>
@@ -6236,10 +6288,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6250,7 +6302,7 @@
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -6259,23 +6311,19 @@
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
@@ -6323,25 +6371,25 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>75</v>
@@ -6349,21 +6397,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -6375,15 +6423,17 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -6420,37 +6470,37 @@
         <v>75</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>75</v>
@@ -6458,14 +6508,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6481,21 +6531,23 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>112</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
       </c>
@@ -6531,19 +6583,19 @@
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6555,13 +6607,13 @@
         <v>98</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>75</v>
@@ -6569,10 +6621,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6592,23 +6644,19 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -6656,7 +6704,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6665,16 +6713,16 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
@@ -6682,21 +6730,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -6705,19 +6753,19 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>111</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6755,37 +6803,37 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -6793,10 +6841,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6804,7 +6852,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>85</v>
@@ -6819,19 +6867,19 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -6841,7 +6889,7 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>303</v>
+        <v>75</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>75</v>
@@ -6941,11 +6989,9 @@
         <v>309</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O39" t="s" s="2">
         <v>310</v>
       </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -7030,7 +7076,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>85</v>
@@ -7045,19 +7091,19 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -7067,7 +7113,7 @@
         <v>75</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>75</v>
+        <v>319</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>75</v>
@@ -7167,10 +7213,10 @@
         <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -7219,7 +7265,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7237,7 +7283,7 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -7245,10 +7291,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="B42" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7271,7 +7317,7 @@
         <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>332</v>
@@ -7296,43 +7342,43 @@
         <v>75</v>
       </c>
       <c r="T42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF42" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7350,7 +7396,7 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -7358,10 +7404,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7387,15 +7433,17 @@
         <v>103</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
       </c>
@@ -7407,43 +7455,43 @@
         <v>75</v>
       </c>
       <c r="T43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7461,7 +7509,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -7469,10 +7517,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7495,18 +7543,20 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -7518,7 +7568,7 @@
         <v>75</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>75</v>
@@ -7566,13 +7616,13 @@
         <v>98</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -7580,10 +7630,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7606,16 +7656,16 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7629,7 +7679,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7665,7 +7715,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7677,13 +7727,13 @@
         <v>98</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -7691,14 +7741,12 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
@@ -7710,7 +7758,7 @@
         <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -7719,18 +7767,18 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>232</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>235</v>
-      </c>
+      <c r="N46" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -7778,36 +7826,36 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>231</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>368</v>
+        <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>237</v>
+        <v>371</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>243</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7827,18 +7875,20 @@
         <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>103</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>104</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7887,7 +7937,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>106</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7896,16 +7946,16 @@
         <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>107</v>
+        <v>380</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>75</v>
@@ -7913,44 +7963,46 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>110</v>
+        <v>248</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>111</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -7986,19 +8038,19 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>117</v>
+        <v>247</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8010,24 +8062,24 @@
         <v>98</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>75</v>
+        <v>384</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>101</v>
+        <v>253</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>75</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8044,26 +8096,22 @@
         <v>75</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>248</v>
+        <v>104</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -8087,13 +8135,13 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>253</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -8111,7 +8159,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8120,16 +8168,16 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>75</v>
@@ -8137,46 +8185,44 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -8200,49 +8246,49 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>255</v>
+        <v>101</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
@@ -8250,10 +8296,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8270,22 +8316,26 @@
         <v>75</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>104</v>
+        <v>264</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -8309,13 +8359,13 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>75</v>
+        <v>269</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -8333,7 +8383,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>106</v>
+        <v>270</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8342,16 +8392,16 @@
         <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>107</v>
+        <v>271</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>75</v>
@@ -8359,44 +8409,46 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>110</v>
+        <v>274</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>112</v>
+        <v>276</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>277</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
@@ -8420,49 +8472,49 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>279</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>280</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>117</v>
+        <v>281</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>101</v>
+        <v>271</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>75</v>
@@ -8470,10 +8522,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8484,7 +8536,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -8493,23 +8545,19 @@
         <v>75</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>272</v>
+        <v>104</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
       </c>
@@ -8557,25 +8605,25 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>276</v>
+        <v>106</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>277</v>
+        <v>107</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>75</v>
@@ -8583,21 +8631,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -8609,15 +8657,17 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8654,37 +8704,37 @@
         <v>75</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>75</v>
@@ -8692,14 +8742,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8715,21 +8765,23 @@
         <v>75</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>112</v>
+        <v>289</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
       </c>
@@ -8765,19 +8817,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8789,13 +8841,13 @@
         <v>98</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>101</v>
+        <v>293</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>75</v>
@@ -8803,10 +8855,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8826,23 +8878,19 @@
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>284</v>
+        <v>104</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
       </c>
@@ -8890,7 +8938,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>288</v>
+        <v>106</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -8899,16 +8947,16 @@
         <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>75</v>
@@ -8916,21 +8964,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -8939,19 +8987,19 @@
         <v>75</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>292</v>
+        <v>111</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>293</v>
+        <v>112</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>294</v>
+        <v>113</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8989,37 +9037,37 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>295</v>
+        <v>117</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>296</v>
+        <v>101</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>75</v>
@@ -9027,10 +9075,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9038,7 +9086,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>85</v>
@@ -9053,19 +9101,19 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -9075,7 +9123,7 @@
         <v>75</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>381</v>
+        <v>75</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>75</v>
@@ -9140,7 +9188,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>307</v>
@@ -9175,11 +9223,9 @@
         <v>309</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O59" t="s" s="2">
         <v>310</v>
       </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
       </c>
@@ -9253,7 +9299,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>314</v>
@@ -9264,7 +9310,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>85</v>
@@ -9279,19 +9325,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -9301,7 +9347,7 @@
         <v>75</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>75</v>
+        <v>397</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>75</v>
@@ -9366,7 +9412,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>323</v>
@@ -9401,10 +9447,10 @@
         <v>325</v>
       </c>
       <c r="N61" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>75</v>
@@ -9453,7 +9499,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9471,7 +9517,7 @@
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>75</v>
@@ -9479,10 +9525,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9505,7 +9551,7 @@
         <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>132</v>
+        <v>331</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>332</v>
@@ -9530,43 +9576,43 @@
         <v>75</v>
       </c>
       <c r="T62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9584,7 +9630,7 @@
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -9592,10 +9638,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9621,15 +9667,17 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9641,43 +9689,43 @@
         <v>75</v>
       </c>
       <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9695,7 +9743,7 @@
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
@@ -9703,10 +9751,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9729,18 +9777,20 @@
         <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>75</v>
       </c>
@@ -9752,7 +9802,7 @@
         <v>75</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>75</v>
@@ -9800,13 +9850,13 @@
         <v>98</v>
       </c>
       <c r="AJ64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL64" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -9814,10 +9864,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9840,16 +9890,16 @@
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9863,7 +9913,7 @@
         <v>75</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>75</v>
@@ -9899,7 +9949,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9911,13 +9961,13 @@
         <v>98</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
@@ -9925,10 +9975,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9945,22 +9995,22 @@
         <v>75</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>365</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9986,13 +10036,13 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>392</v>
+        <v>75</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>393</v>
+        <v>75</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -10010,7 +10060,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10022,24 +10072,24 @@
         <v>98</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>394</v>
+        <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>396</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10053,7 +10103,7 @@
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>75</v>
@@ -10062,16 +10112,16 @@
         <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>144</v>
+        <v>374</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10097,11 +10147,13 @@
         <v>75</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>401</v>
+        <v>75</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -10119,7 +10171,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10131,24 +10183,24 @@
         <v>98</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>99</v>
+        <v>379</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>402</v>
+        <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>396</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10162,25 +10214,25 @@
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>406</v>
+        <v>317</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10206,13 +10258,13 @@
         <v>75</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>75</v>
+        <v>408</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>75</v>
+        <v>409</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -10230,7 +10282,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10245,21 +10297,21 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>75</v>
+        <v>412</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10270,32 +10322,30 @@
         <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
       </c>
@@ -10319,37 +10369,35 @@
         <v>75</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>75</v>
+        <v>417</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>98</v>
@@ -10358,25 +10406,23 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>75</v>
+        <v>418</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>408</v>
+        <v>152</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>75</v>
+        <v>412</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C70" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
@@ -10394,23 +10440,21 @@
         <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
       </c>
@@ -10458,13 +10502,13 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>98</v>
@@ -10473,10 +10517,10 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>75</v>
@@ -10484,10 +10528,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10498,31 +10542,31 @@
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>301</v>
+        <v>428</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -10559,25 +10603,25 @@
         <v>75</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>75</v>
+        <v>430</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>98</v>
@@ -10586,10 +10630,10 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>421</v>
+        <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>75</v>
@@ -10597,12 +10641,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
@@ -10614,28 +10660,28 @@
         <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10660,37 +10706,37 @@
         <v>75</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>423</v>
-      </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>98</v>
@@ -10699,21 +10745,21 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>75</v>
+        <v>432</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>430</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10736,18 +10782,20 @@
         <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>258</v>
+        <v>103</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
       </c>
@@ -10771,11 +10819,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>435</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -10793,13 +10843,13 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>98</v>
@@ -10808,21 +10858,21 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>430</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10833,19 +10883,19 @@
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J74" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K74" t="s" s="2">
-        <v>439</v>
+        <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>440</v>
@@ -10853,8 +10903,12 @@
       <c r="M74" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="N74" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10878,13 +10932,13 @@
         <v>75</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>75</v>
+        <v>441</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>75</v>
+        <v>444</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>75</v>
@@ -10902,36 +10956,36 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>442</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>443</v>
+        <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>75</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10945,24 +10999,26 @@
         <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>448</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10987,13 +11043,11 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>75</v>
+        <v>451</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -11011,36 +11065,36 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>447</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>75</v>
+        <v>452</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>107</v>
+        <v>453</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>75</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11048,13 +11102,13 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
@@ -11063,13 +11117,13 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>455</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>198</v>
+        <v>456</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>199</v>
+        <v>457</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11108,19 +11162,19 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>454</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11132,13 +11186,13 @@
         <v>98</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>458</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>75</v>
+        <v>459</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>75</v>
+        <v>460</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
@@ -11146,26 +11200,24 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>461</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>75</v>
@@ -11174,13 +11226,13 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>449</v>
+        <v>103</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>450</v>
+        <v>104</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>451</v>
+        <v>105</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11231,25 +11283,25 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>75</v>
@@ -11257,26 +11309,24 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C78" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
@@ -11285,13 +11335,13 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>454</v>
+        <v>110</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>198</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>199</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11330,16 +11380,16 @@
         <v>75</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>117</v>
@@ -11368,13 +11418,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>75</v>
@@ -11396,13 +11446,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11479,12 +11529,14 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="C80" s="2"/>
+      <c r="C80" t="s" s="2">
+        <v>469</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
@@ -11496,26 +11548,24 @@
         <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>173</v>
+        <v>470</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -11540,13 +11590,13 @@
         <v>75</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>465</v>
+        <v>75</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>466</v>
+        <v>75</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11564,25 +11614,25 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>467</v>
+        <v>117</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>468</v>
+        <v>98</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>75</v>
@@ -11590,12 +11640,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
@@ -11613,23 +11665,19 @@
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>475</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
@@ -11677,25 +11725,25 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>475</v>
+        <v>117</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>476</v>
+        <v>75</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>477</v>
+        <v>75</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>75</v>
@@ -11723,7 +11771,7 @@
         <v>75</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>86</v>
@@ -11738,11 +11786,9 @@
         <v>480</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>75</v>
       </c>
@@ -11769,37 +11815,37 @@
         <v>164</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="Z82" t="s" s="2">
+      <c r="AG82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI82" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>99</v>
@@ -11808,7 +11854,7 @@
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>75</v>
@@ -11816,10 +11862,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11827,13 +11873,13 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>75</v>
@@ -11842,18 +11888,20 @@
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="N83" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>75</v>
       </c>
@@ -11901,7 +11949,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -11916,10 +11964,10 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>75</v>
+        <v>492</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>107</v>
+        <v>493</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>75</v>
@@ -11927,10 +11975,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11947,24 +11995,26 @@
         <v>75</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J84" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>349</v>
+        <v>173</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>75</v>
       </c>
@@ -11988,13 +12038,13 @@
         <v>75</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>75</v>
+        <v>499</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -12012,7 +12062,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12024,13 +12074,13 @@
         <v>98</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>354</v>
+        <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>75</v>
@@ -12038,10 +12088,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12061,23 +12111,21 @@
         <v>75</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>75</v>
       </c>
@@ -12125,7 +12173,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12140,10 +12188,10 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>504</v>
+        <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>505</v>
+        <v>107</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
@@ -12151,10 +12199,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12174,18 +12222,20 @@
         <v>75</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>103</v>
+        <v>365</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>104</v>
+        <v>510</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -12234,7 +12284,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>106</v>
+        <v>512</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12243,16 +12293,16 @@
         <v>85</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>107</v>
+        <v>513</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
@@ -12260,21 +12310,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>75</v>
@@ -12286,18 +12336,20 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>110</v>
+        <v>515</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>111</v>
+        <v>516</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>112</v>
+        <v>517</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -12333,37 +12385,37 @@
         <v>75</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>117</v>
+        <v>514</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>75</v>
+        <v>520</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>101</v>
+        <v>521</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
@@ -12371,10 +12423,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12391,26 +12443,22 @@
         <v>75</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>509</v>
+        <v>104</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
       </c>
@@ -12422,7 +12470,7 @@
         <v>75</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>513</v>
+        <v>75</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>75</v>
@@ -12434,13 +12482,13 @@
         <v>75</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>514</v>
+        <v>75</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>515</v>
+        <v>75</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>75</v>
@@ -12458,7 +12506,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>516</v>
+        <v>106</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12467,16 +12515,16 @@
         <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>486</v>
+        <v>107</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>75</v>
@@ -12484,21 +12532,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>75</v>
@@ -12507,19 +12555,19 @@
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>518</v>
+        <v>111</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>519</v>
+        <v>112</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>520</v>
+        <v>113</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12533,7 +12581,7 @@
         <v>75</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>521</v>
+        <v>75</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>75</v>
@@ -12545,49 +12593,49 @@
         <v>75</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>522</v>
+        <v>75</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>523</v>
+        <v>75</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>524</v>
+        <v>117</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>486</v>
+        <v>101</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -12595,10 +12643,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12615,25 +12663,25 @@
         <v>75</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -12646,25 +12694,25 @@
         <v>75</v>
       </c>
       <c r="T90" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y90" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="U90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="Z90" t="s" s="2">
-        <v>75</v>
+        <v>531</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -12682,7 +12730,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12700,7 +12748,7 @@
         <v>75</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>75</v>
@@ -12722,7 +12770,7 @@
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>75</v>
@@ -12734,7 +12782,7 @@
         <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>534</v>
@@ -12743,7 +12791,7 @@
         <v>535</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>301</v>
+        <v>536</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12757,7 +12805,7 @@
         <v>75</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>75</v>
@@ -12769,13 +12817,13 @@
         <v>75</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>75</v>
+        <v>538</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>75</v>
+        <v>539</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>75</v>
@@ -12793,13 +12841,13 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>98</v>
@@ -12811,7 +12859,7 @@
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>538</v>
+        <v>502</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>75</v>
@@ -12819,10 +12867,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12842,19 +12890,23 @@
         <v>75</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>104</v>
+        <v>542</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
       </c>
@@ -12866,7 +12918,7 @@
         <v>75</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>75</v>
+        <v>546</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>75</v>
@@ -12902,7 +12954,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>106</v>
+        <v>547</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12911,16 +12963,16 @@
         <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>107</v>
+        <v>548</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>75</v>
@@ -12928,14 +12980,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12951,19 +13003,19 @@
         <v>75</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>111</v>
+        <v>550</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>112</v>
+        <v>551</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>113</v>
+        <v>317</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12977,7 +13029,7 @@
         <v>75</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>75</v>
+        <v>552</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>75</v>
@@ -13001,19 +13053,19 @@
         <v>75</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>117</v>
+        <v>553</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13025,13 +13077,13 @@
         <v>98</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>101</v>
+        <v>554</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>75</v>
@@ -13039,14 +13091,12 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>542</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>75</v>
       </c>
@@ -13058,7 +13108,7 @@
         <v>85</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>75</v>
@@ -13067,13 +13117,13 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>543</v>
+        <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>544</v>
+        <v>104</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>545</v>
+        <v>105</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13124,25 +13174,25 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>546</v>
+        <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>75</v>
@@ -13150,26 +13200,24 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>75</v>
@@ -13178,15 +13226,17 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>550</v>
+        <v>110</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>551</v>
+        <v>111</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -13223,16 +13273,16 @@
         <v>75</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF95" t="s" s="2">
         <v>117</v>
@@ -13250,10 +13300,10 @@
         <v>118</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>553</v>
+        <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>554</v>
+        <v>101</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>75</v>
@@ -13261,13 +13311,13 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>75</v>
@@ -13289,13 +13339,13 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13361,10 +13411,10 @@
         <v>118</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>75</v>
@@ -13372,13 +13422,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>75</v>
@@ -13400,13 +13450,13 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13472,10 +13522,10 @@
         <v>118</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>75</v>
@@ -13483,13 +13533,13 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>75</v>
@@ -13511,13 +13561,13 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13583,10 +13633,10 @@
         <v>118</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>75</v>
@@ -13594,12 +13644,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
@@ -13611,7 +13663,7 @@
         <v>85</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>75</v>
@@ -13620,13 +13672,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>87</v>
+        <v>580</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>104</v>
+        <v>581</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>105</v>
+        <v>582</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13677,25 +13729,25 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>75</v>
+        <v>583</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>107</v>
+        <v>584</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>75</v>
@@ -13703,12 +13755,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
@@ -13717,10 +13771,10 @@
         <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>75</v>
@@ -13729,13 +13783,13 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>110</v>
+        <v>587</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>198</v>
+        <v>588</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>199</v>
+        <v>589</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13774,16 +13828,16 @@
         <v>75</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>117</v>
@@ -13795,16 +13849,16 @@
         <v>77</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>118</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>75</v>
+        <v>590</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>75</v>
+        <v>591</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>75</v>
@@ -13812,10 +13866,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13823,7 +13877,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>85</v>
@@ -13838,24 +13892,22 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>582</v>
+        <v>104</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>585</v>
+        <v>75</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>75</v>
@@ -13897,16 +13949,16 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>586</v>
+        <v>106</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>75</v>
@@ -13915,7 +13967,7 @@
         <v>75</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>75</v>
@@ -13923,10 +13975,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>587</v>
+        <v>594</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13934,10 +13986,10 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>75</v>
@@ -13949,13 +14001,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>589</v>
+        <v>198</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>590</v>
+        <v>199</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13982,47 +14034,49 @@
         <v>75</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>591</v>
+        <v>75</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>592</v>
+        <v>117</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>593</v>
+        <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>75</v>
@@ -14030,26 +14084,24 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>75</v>
@@ -14058,22 +14110,24 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>596</v>
+        <v>132</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>75</v>
+        <v>601</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>75</v>
@@ -14115,25 +14169,25 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>117</v>
+        <v>602</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>599</v>
+        <v>75</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>600</v>
+        <v>101</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>75</v>
@@ -14141,26 +14195,24 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>75</v>
@@ -14169,13 +14221,13 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>603</v>
+        <v>103</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14202,13 +14254,11 @@
         <v>75</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>75</v>
+        <v>607</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>75</v>
@@ -14226,25 +14276,25 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>117</v>
+        <v>608</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>98</v>
+        <v>609</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>606</v>
+        <v>75</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>607</v>
+        <v>101</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>75</v>
@@ -14252,13 +14302,13 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>75</v>
@@ -14280,13 +14330,13 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14352,10 +14402,10 @@
         <v>118</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>75</v>
@@ -14363,12 +14413,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="D106" t="s" s="2">
         <v>75</v>
       </c>
@@ -14380,7 +14432,7 @@
         <v>85</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>75</v>
@@ -14389,13 +14441,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>103</v>
+        <v>619</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14419,7 +14471,7 @@
         <v>75</v>
       </c>
       <c r="W106" t="s" s="2">
-        <v>615</v>
+        <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
         <v>75</v>
@@ -14446,25 +14498,25 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>616</v>
+        <v>117</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>75</v>
+        <v>622</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14472,14 +14524,16 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="D107" t="s" s="2">
-        <v>618</v>
+        <v>75</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14489,26 +14543,24 @@
         <v>85</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>626</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -14521,7 +14573,7 @@
         <v>75</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>621</v>
+        <v>75</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>75</v>
@@ -14557,25 +14609,25 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>622</v>
+        <v>117</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>624</v>
+        <v>75</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
@@ -14583,14 +14635,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>626</v>
+        <v>75</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14606,20 +14658,18 @@
         <v>75</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>75</v>
@@ -14632,7 +14682,7 @@
         <v>75</v>
       </c>
       <c r="T108" t="s" s="2">
-        <v>630</v>
+        <v>75</v>
       </c>
       <c r="U108" t="s" s="2">
         <v>75</v>
@@ -14641,7 +14691,7 @@
         <v>75</v>
       </c>
       <c r="W108" t="s" s="2">
-        <v>75</v>
+        <v>631</v>
       </c>
       <c r="X108" t="s" s="2">
         <v>75</v>
@@ -14668,7 +14718,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14677,16 +14727,16 @@
         <v>85</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>632</v>
+        <v>75</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>75</v>
@@ -14729,7 +14779,7 @@
         <v>636</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14743,7 +14793,7 @@
         <v>75</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>75</v>
+        <v>637</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>75</v>
@@ -14779,7 +14829,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14794,10 +14844,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>75</v>
+        <v>639</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>75</v>
@@ -14805,14 +14855,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14834,13 +14884,13 @@
         <v>103</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>301</v>
+        <v>645</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14854,7 +14904,7 @@
         <v>75</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>75</v>
@@ -14890,7 +14940,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14905,10 +14955,10 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>645</v>
+        <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14916,14 +14966,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>75</v>
+        <v>650</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -14945,13 +14995,13 @@
         <v>103</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>650</v>
+        <v>317</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15001,7 +15051,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -15019,7 +15069,7 @@
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>75</v>
@@ -15027,14 +15077,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>75</v>
+        <v>656</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15053,20 +15103,18 @@
         <v>86</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>349</v>
+        <v>103</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>656</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
       </c>
@@ -15078,7 +15126,7 @@
         <v>75</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>75</v>
@@ -15114,7 +15162,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15126,13 +15174,13 @@
         <v>98</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>354</v>
+        <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>497</v>
+        <v>662</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>75</v>
@@ -15140,10 +15188,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15166,20 +15214,18 @@
         <v>86</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>258</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>662</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
       </c>
@@ -15203,13 +15249,13 @@
         <v>75</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>663</v>
+        <v>75</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>664</v>
+        <v>75</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>75</v>
@@ -15227,7 +15273,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15245,18 +15291,18 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>430</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15276,20 +15322,22 @@
         <v>75</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>667</v>
+        <v>365</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>671</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O114" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15302,7 +15350,7 @@
         <v>75</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>75</v>
+        <v>673</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>75</v>
@@ -15338,7 +15386,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15350,13 +15398,13 @@
         <v>98</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>99</v>
+        <v>370</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>671</v>
+        <v>75</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>672</v>
+        <v>513</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>75</v>
@@ -15364,10 +15412,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15387,19 +15435,23 @@
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>103</v>
+        <v>274</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>104</v>
+        <v>676</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>75</v>
       </c>
@@ -15423,13 +15475,13 @@
         <v>75</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>75</v>
+        <v>679</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>75</v>
+        <v>680</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>75</v>
@@ -15447,7 +15499,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>106</v>
+        <v>675</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15456,38 +15508,38 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>107</v>
+        <v>681</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>75</v>
+        <v>446</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>75</v>
@@ -15499,18 +15551,18 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>110</v>
+        <v>683</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>111</v>
+        <v>684</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>685</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>686</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15546,37 +15598,37 @@
         <v>75</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>117</v>
+        <v>682</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>75</v>
+        <v>687</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>101</v>
+        <v>688</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>75</v>
@@ -15584,14 +15636,12 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>689</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
@@ -15603,7 +15653,7 @@
         <v>85</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
@@ -15612,13 +15662,13 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>677</v>
+        <v>103</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>678</v>
+        <v>104</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>679</v>
+        <v>105</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15669,25 +15719,25 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>75</v>
@@ -15695,14 +15745,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>681</v>
+        <v>109</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15715,26 +15765,24 @@
         <v>75</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>110</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>682</v>
+        <v>111</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>683</v>
+        <v>112</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="O118" t="s" s="2">
-        <v>229</v>
-      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>75</v>
       </c>
@@ -15770,19 +15818,19 @@
         <v>75</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>684</v>
+        <v>117</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15808,24 +15856,26 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>690</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>692</v>
+      </c>
       <c r="D119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>75</v>
@@ -15834,17 +15884,15 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>689</v>
-      </c>
+        <v>695</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -15893,25 +15941,25 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>685</v>
+        <v>117</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>690</v>
+        <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>691</v>
+        <v>75</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>75</v>
@@ -15919,44 +15967,46 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>75</v>
+        <v>697</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>686</v>
+        <v>110</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="O120" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>75</v>
       </c>
@@ -16004,25 +16054,25 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>695</v>
+        <v>75</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>691</v>
+        <v>101</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>75</v>
@@ -16030,10 +16080,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16041,7 +16091,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>85</v>
@@ -16056,16 +16106,16 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>689</v>
+        <v>705</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16115,10 +16165,10 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>85</v>
@@ -16130,10 +16180,10 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>75</v>
+        <v>706</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>75</v>
@@ -16141,10 +16191,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16152,35 +16202,33 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="O122" t="s" s="2">
-        <v>704</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>75</v>
       </c>
@@ -16228,10 +16276,10 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>699</v>
+        <v>708</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>85</v>
@@ -16240,13 +16288,13 @@
         <v>98</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>75</v>
+        <v>711</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>75</v>
@@ -16254,10 +16302,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16271,7 +16319,7 @@
         <v>85</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
@@ -16280,20 +16328,18 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>711</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>75</v>
       </c>
@@ -16341,7 +16387,7 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16353,13 +16399,13 @@
         <v>98</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>75</v>
@@ -16367,10 +16413,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16381,30 +16427,32 @@
         <v>76</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>667</v>
+        <v>716</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="O124" s="2"/>
+        <v>719</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>720</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>75</v>
       </c>
@@ -16452,25 +16500,25 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>99</v>
+        <v>379</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>75</v>
@@ -16478,10 +16526,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16495,7 +16543,7 @@
         <v>85</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
@@ -16504,16 +16552,20 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>103</v>
+        <v>723</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>104</v>
+        <v>724</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>725</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>727</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16561,7 +16613,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>106</v>
+        <v>722</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16570,16 +16622,16 @@
         <v>85</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>75</v>
+        <v>379</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>107</v>
+        <v>728</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>75</v>
@@ -16587,14 +16639,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>719</v>
+        <v>729</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16613,16 +16665,16 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>110</v>
+        <v>683</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>111</v>
+        <v>730</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>112</v>
+        <v>731</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>113</v>
+        <v>732</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -16660,19 +16712,19 @@
         <v>75</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>117</v>
+        <v>729</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16684,13 +16736,13 @@
         <v>98</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>101</v>
+        <v>733</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>75</v>
@@ -16698,46 +16750,42 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>681</v>
+        <v>75</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>682</v>
+        <v>104</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16785,25 +16833,25 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>684</v>
+        <v>106</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>118</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>75</v>
@@ -16811,14 +16859,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16837,16 +16885,16 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>722</v>
+        <v>111</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>723</v>
+        <v>112</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>301</v>
+        <v>113</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -16872,31 +16920,31 @@
         <v>75</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="Y128" t="s" s="2">
-        <v>724</v>
+        <v>75</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>725</v>
+        <v>75</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>721</v>
+        <v>117</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -16908,13 +16956,13 @@
         <v>98</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>717</v>
+        <v>101</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>75</v>
@@ -16922,42 +16970,46 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>726</v>
+        <v>736</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>75</v>
+        <v>697</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I129" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>315</v>
+        <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>727</v>
+        <v>698</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+        <v>699</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -17005,25 +17057,25 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>717</v>
+        <v>101</v>
       </c>
       <c r="AM129" t="s" s="2">
         <v>75</v>
@@ -17031,10 +17083,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17045,7 +17097,7 @@
         <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>75</v>
@@ -17057,15 +17109,17 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>730</v>
+        <v>173</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>739</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>75</v>
@@ -17090,13 +17144,13 @@
         <v>75</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>75</v>
+        <v>740</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>75</v>
+        <v>741</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>75</v>
@@ -17114,13 +17168,13 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>98</v>
@@ -17132,7 +17186,7 @@
         <v>75</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>75</v>
@@ -17140,10 +17194,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17166,13 +17220,13 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>730</v>
+        <v>331</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>735</v>
+        <v>744</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17223,7 +17277,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17241,7 +17295,7 @@
         <v>75</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>717</v>
+        <v>733</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>75</v>
@@ -17249,10 +17303,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17275,17 +17329,15 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
+        <v>746</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>737</v>
+        <v>747</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>75</v>
@@ -17334,7 +17386,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17352,7 +17404,7 @@
         <v>75</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>107</v>
+        <v>733</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>75</v>
@@ -17360,10 +17412,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17374,7 +17426,7 @@
         <v>76</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>75</v>
@@ -17386,20 +17438,16 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>743</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>75</v>
       </c>
@@ -17447,32 +17495,256 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>739</v>
+        <v>749</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="AM133" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="P135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM133">
+  <autoFilter ref="A1:AM135">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17482,7 +17754,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI132">
+  <conditionalFormatting sqref="A2:AI134">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
